--- a/public/templates/Suppliments or Nutraceuticals _Product_Upload_Template_v0.1.xlsx
+++ b/public/templates/Suppliments or Nutraceuticals _Product_Upload_Template_v0.1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yash\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TiaMeds Market Platform\Seller Module\Data Upload - Excel Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705A6A1D-4D34-43EE-9C28-CD939720BB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D62B53C-73F6-4713-8658-ADA2E2DD6CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,11 @@
     <sheet name="Suppliments or Nutraceuticals " sheetId="1" r:id="rId1"/>
     <sheet name="Masters" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>Therapeutic Category*</t>
   </si>
@@ -45,6 +48,20 @@
     <t>Product Name*</t>
   </si>
   <si>
+    <r>
+      <t>Active Ingredients</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFEE0000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
     <t>Dosage Form*</t>
   </si>
   <si>
@@ -60,6 +77,37 @@
     <t>Product Image URL*</t>
   </si>
   <si>
+    <r>
+      <t>Nutritional Information Table</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFEE0000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <t>Recommended Daily Allowance (RDA %)</t>
+  </si>
+  <si>
+    <r>
+      <t>Veg / Non-Veg Indicator</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFEE0000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
     <t>Product Marketing URL</t>
   </si>
   <si>
@@ -72,12 +120,18 @@
     <t>Pack Size (Auto)</t>
   </si>
   <si>
+    <t>Minimum Order Qty*</t>
+  </si>
+  <si>
     <t>Max Order Qty*</t>
   </si>
   <si>
     <t>Batch / Lot Number*</t>
   </si>
   <si>
+    <t>Manufacturer Name*</t>
+  </si>
+  <si>
     <t>Manufacturing Date*</t>
   </si>
   <si>
@@ -90,6 +144,12 @@
     <t>Stock Quantity*</t>
   </si>
   <si>
+    <t>Date of Entry*</t>
+  </si>
+  <si>
+    <t>Price per Unit*</t>
+  </si>
+  <si>
     <t>MRP (INR)*</t>
   </si>
   <si>
@@ -99,112 +159,16 @@
     <t>Additional Discount</t>
   </si>
   <si>
+    <t>Final Price (Auto update)</t>
+  </si>
+  <si>
     <t>GST %</t>
   </si>
   <si>
     <t>HSN Code*</t>
   </si>
   <si>
-    <t>TherapeuticCategory</t>
-  </si>
-  <si>
-    <t>TherapeuticSubCategory</t>
-  </si>
-  <si>
-    <t>DosageForm</t>
-  </si>
-  <si>
-    <t>Strength</t>
-  </si>
-  <si>
-    <t>PackagingUnit</t>
-  </si>
-  <si>
-    <t>StorageCondition</t>
-  </si>
-  <si>
-    <t>Analgesic</t>
-  </si>
-  <si>
-    <t>Pain Relief</t>
-  </si>
-  <si>
-    <t>Tablet</t>
-  </si>
-  <si>
-    <t>250mg</t>
-  </si>
-  <si>
-    <t>Strip</t>
-  </si>
-  <si>
-    <t>Room Temperature</t>
-  </si>
-  <si>
-    <t>Antibiotic</t>
-  </si>
-  <si>
-    <t>Broad Spectrum</t>
-  </si>
-  <si>
-    <t>Capsule</t>
-  </si>
-  <si>
-    <t>500mg</t>
-  </si>
-  <si>
-    <t>Bottle</t>
-  </si>
-  <si>
-    <t>2-8°C</t>
-  </si>
-  <si>
-    <t>Antiviral</t>
-  </si>
-  <si>
-    <t>Respiratory</t>
-  </si>
-  <si>
-    <t>Syrup</t>
-  </si>
-  <si>
-    <t>650mg</t>
-  </si>
-  <si>
-    <t>Box</t>
-  </si>
-  <si>
-    <t>Keep Dry Place</t>
-  </si>
-  <si>
-    <t>Antifungal</t>
-  </si>
-  <si>
-    <t>Dermatology</t>
-  </si>
-  <si>
-    <t>Injection</t>
-  </si>
-  <si>
-    <t>5ml</t>
-  </si>
-  <si>
-    <t>Vial</t>
-  </si>
-  <si>
-    <t>10ml</t>
-  </si>
-  <si>
-    <t>Minimum Order Qty*</t>
-  </si>
-  <si>
-    <t>Date of Entry*</t>
-  </si>
-  <si>
     <t>Minimum Purchase Quantity</t>
-  </si>
-  <si>
-    <t>Final Price (Auto update)</t>
   </si>
   <si>
     <r>
@@ -223,212 +187,101 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Active Ingredients</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFEE0000"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>*</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Nutritional Information Table</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFEE0000"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>*</t>
-    </r>
-  </si>
-  <si>
-    <t>Recommended Daily Allowance (RDA %)</t>
-  </si>
-  <si>
-    <r>
-      <t>Veg / Non-Veg Indicator</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFEE0000"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>*</t>
-    </r>
-  </si>
-  <si>
-    <t>Manufacturer Name*</t>
-  </si>
-  <si>
-    <t>Price per Unit*</t>
-  </si>
-  <si>
-    <t>Crocin 650</t>
-  </si>
-  <si>
-    <t>Augmentin 625</t>
-  </si>
-  <si>
-    <t>Azithral 500</t>
-  </si>
-  <si>
-    <t>Brufen 400</t>
-  </si>
-  <si>
-    <t>Fluconaz 150</t>
-  </si>
-  <si>
-    <t>Tamiflu 75</t>
-  </si>
-  <si>
-    <t>Amoxil 250 Syrup</t>
-  </si>
-  <si>
-    <t>Canesten Cream</t>
-  </si>
-  <si>
-    <t>Voveron Injection</t>
-  </si>
-  <si>
-    <t>Zovirax 200</t>
-  </si>
-  <si>
-    <t>Paracetamol</t>
-  </si>
-  <si>
-    <t>Amoxicillin + Clavulanic Acid</t>
-  </si>
-  <si>
-    <t>Azithromycin</t>
-  </si>
-  <si>
-    <t>Ibuprofen</t>
-  </si>
-  <si>
-    <t>Fluconazole</t>
-  </si>
-  <si>
-    <t>Oseltamivir</t>
-  </si>
-  <si>
-    <t>Amoxicillin</t>
-  </si>
-  <si>
-    <t>Clotrimazole</t>
-  </si>
-  <si>
-    <t>Diclofenac Sodium</t>
-  </si>
-  <si>
-    <t>Acyclovir</t>
-  </si>
-  <si>
-    <t>Not for children under 12. Avoid alcohol.</t>
-  </si>
-  <si>
-    <t>Prescription only. May cause diarrhea.</t>
-  </si>
-  <si>
-    <t>Prescription only. Avoid antacids.</t>
-  </si>
-  <si>
-    <t>Take with food. Avoid in peptic ulcer.</t>
-  </si>
-  <si>
-    <t>Avoid in liver disease. Single dose.</t>
-  </si>
-  <si>
-    <t>Start within 48hrs of symptoms. Rx only.</t>
-  </si>
-  <si>
-    <t>Shake well before use. Rx only.</t>
-  </si>
-  <si>
-    <t>External use only. Avoid eyes.</t>
-  </si>
-  <si>
-    <t>IM use only. Avoid in renal impairment.</t>
-  </si>
-  <si>
-    <t>Stay well hydrated. Caution in renal disease.</t>
-  </si>
-  <si>
-    <t>Fever and pain relief tablet</t>
-  </si>
-  <si>
-    <t>Broad spectrum antibiotic for bacterial infections</t>
-  </si>
-  <si>
-    <t>Antibiotic for respiratory tract infections</t>
-  </si>
-  <si>
-    <t>Anti-inflammatory pain relief tablet</t>
-  </si>
-  <si>
-    <t>Antifungal capsule for candida infections</t>
-  </si>
-  <si>
-    <t>Antiviral capsule for influenza treatment</t>
-  </si>
-  <si>
-    <t>Antibiotic syrup for children respiratory infections</t>
-  </si>
-  <si>
-    <t>Antifungal cream for skin infections</t>
-  </si>
-  <si>
-    <t>Injectable NSAID for acute pain management</t>
-  </si>
-  <si>
-    <t>Antiviral tablet for herpes simplex treatment</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Veg</t>
-  </si>
-  <si>
-    <t>Non-Veg</t>
-  </si>
-  <si>
-    <t>GSK Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>Alkem Laboratories</t>
-  </si>
-  <si>
-    <t>Abbott India</t>
-  </si>
-  <si>
-    <t>Cipla Ltd</t>
-  </si>
-  <si>
-    <t>Roche India</t>
-  </si>
-  <si>
-    <t>Bayer India</t>
-  </si>
-  <si>
-    <t>Novartis India</t>
+    <t>TherapeuticCategory</t>
+  </si>
+  <si>
+    <t>TherapeuticSubCategory</t>
+  </si>
+  <si>
+    <t>DosageForm</t>
+  </si>
+  <si>
+    <t>Strength</t>
+  </si>
+  <si>
+    <t>PackagingUnit</t>
+  </si>
+  <si>
+    <t>StorageCondition</t>
+  </si>
+  <si>
+    <t>Analgesic</t>
+  </si>
+  <si>
+    <t>Pain Relief</t>
+  </si>
+  <si>
+    <t>Tablet</t>
+  </si>
+  <si>
+    <t>250mg</t>
+  </si>
+  <si>
+    <t>Strip</t>
+  </si>
+  <si>
+    <t>Room Temperature</t>
+  </si>
+  <si>
+    <t>Antibiotic</t>
+  </si>
+  <si>
+    <t>Broad Spectrum</t>
+  </si>
+  <si>
+    <t>Capsule</t>
+  </si>
+  <si>
+    <t>500mg</t>
+  </si>
+  <si>
+    <t>Bottle</t>
+  </si>
+  <si>
+    <t>2-8°C</t>
+  </si>
+  <si>
+    <t>Antiviral</t>
+  </si>
+  <si>
+    <t>Respiratory</t>
+  </si>
+  <si>
+    <t>Syrup</t>
+  </si>
+  <si>
+    <t>650mg</t>
+  </si>
+  <si>
+    <t>Box</t>
+  </si>
+  <si>
+    <t>Keep Dry Place</t>
+  </si>
+  <si>
+    <t>Antifungal</t>
+  </si>
+  <si>
+    <t>Dermatology</t>
+  </si>
+  <si>
+    <t>Injection</t>
+  </si>
+  <si>
+    <t>5ml</t>
+  </si>
+  <si>
+    <t>Vial</t>
+  </si>
+  <si>
+    <t>10ml</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -464,34 +317,16 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -499,37 +334,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBDD7EE"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBDD7EE"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBDD7EE"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBDD7EE"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -853,1122 +666,282 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG500"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" customWidth="1"/>
-    <col min="4" max="4" width="24.77734375" customWidth="1"/>
-    <col min="5" max="5" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.88671875" customWidth="1"/>
-    <col min="8" max="8" width="41.6640625" customWidth="1"/>
-    <col min="9" max="9" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.33203125" customWidth="1"/>
-    <col min="13" max="13" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.28515625" customWidth="1"/>
+    <col min="13" max="13" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.77734375" customWidth="1"/>
-    <col min="21" max="21" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.7109375" customWidth="1"/>
+    <col min="21" max="21" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="16" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="24.21875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:33" ht="15.6" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="M1" s="5" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="R1" s="5" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="U1" s="5" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Y1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z1" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA1" s="5" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AD1" s="5"/>
-      <c r="AE1" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AF1" s="5" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="2"/>
+      <c r="AE1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" ht="15.6">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
       <c r="AC2" s="1" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
-      <c r="AG2" s="5"/>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J3" t="s">
-        <v>104</v>
-      </c>
-      <c r="K3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L3" t="s">
-        <v>105</v>
-      </c>
-      <c r="N3" t="s">
         <v>33</v>
       </c>
-      <c r="O3">
-        <v>10</v>
-      </c>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+    </row>
+    <row r="3" spans="1:33">
       <c r="P3" t="str">
         <f t="shared" ref="P3:P65" si="0">IF(AND(N3&lt;&gt;"",O3&lt;&gt;""),N3&amp;" x "&amp;O3,"")</f>
-        <v>Strip x 10</v>
-      </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>10</v>
-      </c>
-      <c r="T3" t="s">
-        <v>107</v>
-      </c>
-      <c r="U3" s="4">
-        <v>45292</v>
-      </c>
-      <c r="V3" s="4">
-        <v>46023</v>
-      </c>
-      <c r="W3" t="s">
-        <v>34</v>
-      </c>
-      <c r="X3">
-        <v>500</v>
-      </c>
-      <c r="Y3" s="4">
-        <v>45717</v>
-      </c>
-      <c r="Z3" s="4">
-        <v>12</v>
-      </c>
-      <c r="AA3" s="4">
-        <v>120</v>
-      </c>
-      <c r="AB3" s="4">
-        <v>5</v>
-      </c>
-      <c r="AC3" s="4">
-        <v>10</v>
-      </c>
-      <c r="AD3" s="4">
-        <v>10</v>
-      </c>
-      <c r="AE3">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
         <f t="shared" ref="AE3:AE65" si="1">IF(AA3="","",AA3-(AA3*AB3/100)-AC3)</f>
-        <v>104</v>
-      </c>
-      <c r="AF3">
-        <v>12</v>
-      </c>
-      <c r="AG3">
-        <v>30049099</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" t="s">
-        <v>85</v>
-      </c>
-      <c r="H4" t="s">
-        <v>95</v>
-      </c>
-      <c r="J4" t="s">
-        <v>104</v>
-      </c>
-      <c r="K4" t="s">
-        <v>104</v>
-      </c>
-      <c r="L4" t="s">
-        <v>105</v>
-      </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4">
-        <v>10</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:33">
       <c r="P4" t="str">
         <f t="shared" si="0"/>
-        <v>Strip x 10</v>
-      </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>5</v>
-      </c>
-      <c r="T4" t="s">
-        <v>107</v>
-      </c>
-      <c r="U4" s="4">
-        <v>45323</v>
-      </c>
-      <c r="V4" s="4">
-        <v>46054</v>
-      </c>
-      <c r="W4" t="s">
-        <v>40</v>
-      </c>
-      <c r="X4">
-        <v>200</v>
-      </c>
-      <c r="Y4" s="4">
-        <v>45717</v>
-      </c>
-      <c r="Z4">
-        <v>35</v>
-      </c>
-      <c r="AA4">
-        <v>350</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>10</v>
-      </c>
-      <c r="AD4">
-        <v>5</v>
-      </c>
-      <c r="AE4">
-        <f t="shared" si="1"/>
-        <v>340</v>
-      </c>
-      <c r="AF4">
-        <v>12</v>
-      </c>
-      <c r="AG4">
-        <v>30041090</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H5" t="s">
-        <v>96</v>
-      </c>
-      <c r="J5" t="s">
-        <v>104</v>
-      </c>
-      <c r="K5" t="s">
-        <v>104</v>
-      </c>
-      <c r="L5" t="s">
-        <v>105</v>
-      </c>
-      <c r="N5" t="s">
-        <v>33</v>
-      </c>
-      <c r="O5">
-        <v>5</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AE4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:33">
       <c r="P5" t="str">
         <f t="shared" si="0"/>
-        <v>Strip x 5</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>3</v>
-      </c>
-      <c r="T5" t="s">
-        <v>108</v>
-      </c>
-      <c r="U5" s="4">
-        <v>45352</v>
-      </c>
-      <c r="V5" s="4">
-        <v>46082</v>
-      </c>
-      <c r="W5" t="s">
-        <v>40</v>
-      </c>
-      <c r="X5">
-        <v>300</v>
-      </c>
-      <c r="Y5" s="4">
-        <v>45717</v>
-      </c>
-      <c r="Z5">
-        <v>45</v>
-      </c>
-      <c r="AA5">
-        <v>225</v>
-      </c>
-      <c r="AB5">
-        <v>10</v>
-      </c>
-      <c r="AC5">
-        <v>10</v>
-      </c>
-      <c r="AD5">
-        <v>5</v>
-      </c>
-      <c r="AE5">
-        <f t="shared" si="1"/>
-        <v>192.5</v>
-      </c>
-      <c r="AF5">
-        <v>12</v>
-      </c>
-      <c r="AG5">
-        <v>30041090</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" t="s">
-        <v>87</v>
-      </c>
-      <c r="H6" t="s">
-        <v>97</v>
-      </c>
-      <c r="J6" t="s">
-        <v>104</v>
-      </c>
-      <c r="K6" t="s">
-        <v>104</v>
-      </c>
-      <c r="L6" t="s">
-        <v>105</v>
-      </c>
-      <c r="N6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O6">
-        <v>15</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AE5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:33">
       <c r="P6" t="str">
         <f t="shared" si="0"/>
-        <v>Strip x 15</v>
-      </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>10</v>
-      </c>
-      <c r="T6" t="s">
-        <v>109</v>
-      </c>
-      <c r="U6" s="4">
-        <v>45306</v>
-      </c>
-      <c r="V6" s="4">
-        <v>46037</v>
-      </c>
-      <c r="W6" t="s">
-        <v>34</v>
-      </c>
-      <c r="X6">
-        <v>400</v>
-      </c>
-      <c r="Y6" s="4">
-        <v>45717</v>
-      </c>
-      <c r="Z6">
-        <v>8</v>
-      </c>
-      <c r="AA6">
-        <v>120</v>
-      </c>
-      <c r="AB6">
-        <v>5</v>
-      </c>
-      <c r="AC6">
-        <v>40</v>
-      </c>
-      <c r="AD6">
-        <v>6</v>
-      </c>
-      <c r="AE6">
-        <f t="shared" si="1"/>
-        <v>74</v>
-      </c>
-      <c r="AF6">
-        <v>12</v>
-      </c>
-      <c r="AG6">
-        <v>30049099</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H7" t="s">
-        <v>98</v>
-      </c>
-      <c r="J7" t="s">
-        <v>104</v>
-      </c>
-      <c r="K7" t="s">
-        <v>104</v>
-      </c>
-      <c r="L7" t="s">
-        <v>106</v>
-      </c>
-      <c r="N7" t="s">
-        <v>45</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AE6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:33">
       <c r="P7" t="str">
         <f t="shared" si="0"/>
-        <v>Box x 1</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>5</v>
-      </c>
-      <c r="T7" t="s">
-        <v>110</v>
-      </c>
-      <c r="U7" s="4">
-        <v>45383</v>
-      </c>
-      <c r="V7" s="4">
-        <v>46113</v>
-      </c>
-      <c r="W7" t="s">
-        <v>46</v>
-      </c>
-      <c r="X7">
-        <v>150</v>
-      </c>
-      <c r="Y7" s="4">
-        <v>45717</v>
-      </c>
-      <c r="Z7">
-        <v>28</v>
-      </c>
-      <c r="AA7">
-        <v>28</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="AF7">
-        <v>12</v>
-      </c>
-      <c r="AG7">
-        <v>30049049</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H8" t="s">
-        <v>99</v>
-      </c>
-      <c r="J8" t="s">
-        <v>104</v>
-      </c>
-      <c r="K8" t="s">
-        <v>104</v>
-      </c>
-      <c r="L8" t="s">
-        <v>106</v>
-      </c>
-      <c r="N8" t="s">
-        <v>45</v>
-      </c>
-      <c r="O8">
-        <v>10</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AE7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:33">
       <c r="P8" t="str">
         <f t="shared" si="0"/>
-        <v>Box x 10</v>
-      </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>2</v>
-      </c>
-      <c r="T8" t="s">
-        <v>111</v>
-      </c>
-      <c r="U8" s="4">
-        <v>45413</v>
-      </c>
-      <c r="V8" s="4">
-        <v>46143</v>
-      </c>
-      <c r="W8" t="s">
-        <v>40</v>
-      </c>
-      <c r="X8">
-        <v>100</v>
-      </c>
-      <c r="Y8" s="4">
-        <v>45717</v>
-      </c>
-      <c r="Z8">
-        <v>220</v>
-      </c>
-      <c r="AA8">
-        <v>2200</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <f t="shared" si="1"/>
-        <v>2200</v>
-      </c>
-      <c r="AF8">
-        <v>5</v>
-      </c>
-      <c r="AG8">
-        <v>30029099</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H9" t="s">
-        <v>100</v>
-      </c>
-      <c r="J9" t="s">
-        <v>104</v>
-      </c>
-      <c r="K9" t="s">
-        <v>104</v>
-      </c>
-      <c r="L9" t="s">
-        <v>105</v>
-      </c>
-      <c r="N9" t="s">
-        <v>39</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AE8" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:33">
       <c r="P9" t="str">
         <f t="shared" si="0"/>
-        <v>Bottle x 1</v>
-      </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>3</v>
-      </c>
-      <c r="T9" t="s">
-        <v>107</v>
-      </c>
-      <c r="U9" s="4">
-        <v>45337</v>
-      </c>
-      <c r="V9" s="4">
-        <v>45884</v>
-      </c>
-      <c r="W9" t="s">
-        <v>40</v>
-      </c>
-      <c r="X9">
-        <v>250</v>
-      </c>
-      <c r="Y9" s="4">
-        <v>45717</v>
-      </c>
-      <c r="Z9">
-        <v>65</v>
-      </c>
-      <c r="AA9">
-        <v>65</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <f t="shared" si="1"/>
-        <v>65</v>
-      </c>
-      <c r="AF9">
-        <v>12</v>
-      </c>
-      <c r="AG9">
-        <v>30041090</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H10" t="s">
-        <v>101</v>
-      </c>
-      <c r="J10" t="s">
-        <v>104</v>
-      </c>
-      <c r="K10" t="s">
-        <v>104</v>
-      </c>
-      <c r="L10" t="s">
-        <v>105</v>
-      </c>
-      <c r="N10" t="s">
-        <v>45</v>
-      </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AE9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:33">
       <c r="P10" t="str">
         <f t="shared" si="0"/>
-        <v>Box x 1</v>
-      </c>
-      <c r="Q10">
-        <v>1</v>
-      </c>
-      <c r="R10">
-        <v>5</v>
-      </c>
-      <c r="T10" t="s">
-        <v>112</v>
-      </c>
-      <c r="U10" s="4">
-        <v>45444</v>
-      </c>
-      <c r="V10" s="4">
-        <v>46174</v>
-      </c>
-      <c r="W10" t="s">
-        <v>34</v>
-      </c>
-      <c r="X10">
-        <v>180</v>
-      </c>
-      <c r="Y10" s="4">
-        <v>45717</v>
-      </c>
-      <c r="Z10">
-        <v>95</v>
-      </c>
-      <c r="AA10">
-        <v>95</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>20</v>
-      </c>
-      <c r="AD10">
-        <v>4</v>
-      </c>
-      <c r="AE10">
-        <f t="shared" si="1"/>
-        <v>75</v>
-      </c>
-      <c r="AF10">
-        <v>18</v>
-      </c>
-      <c r="AG10">
-        <v>30049059</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" t="s">
-        <v>92</v>
-      </c>
-      <c r="H11" t="s">
-        <v>102</v>
-      </c>
-      <c r="J11" t="s">
-        <v>104</v>
-      </c>
-      <c r="K11" t="s">
-        <v>104</v>
-      </c>
-      <c r="L11" t="s">
-        <v>105</v>
-      </c>
-      <c r="N11" t="s">
-        <v>51</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AE10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:33">
       <c r="P11" t="str">
         <f t="shared" si="0"/>
-        <v>Vial x 1</v>
-      </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
-      <c r="R11">
-        <v>5</v>
-      </c>
-      <c r="T11" t="s">
-        <v>113</v>
-      </c>
-      <c r="U11" s="4">
-        <v>45366</v>
-      </c>
-      <c r="V11" s="4">
-        <v>46096</v>
-      </c>
-      <c r="W11" t="s">
-        <v>40</v>
-      </c>
-      <c r="X11">
-        <v>120</v>
-      </c>
-      <c r="Y11" s="4">
-        <v>45717</v>
-      </c>
-      <c r="Z11">
-        <v>22</v>
-      </c>
-      <c r="AA11">
-        <v>22</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <v>15</v>
-      </c>
-      <c r="AD11">
-        <v>3</v>
-      </c>
-      <c r="AE11">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="AF11">
-        <v>12</v>
-      </c>
-      <c r="AG11">
-        <v>30049099</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J12" t="s">
-        <v>104</v>
-      </c>
-      <c r="K12" t="s">
-        <v>104</v>
-      </c>
-      <c r="L12" t="s">
-        <v>105</v>
-      </c>
-      <c r="N12" t="s">
-        <v>33</v>
-      </c>
-      <c r="O12">
-        <v>25</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AE11" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:33">
       <c r="P12" t="str">
         <f t="shared" si="0"/>
-        <v>Strip x 25</v>
-      </c>
-      <c r="Q12">
-        <v>1</v>
-      </c>
-      <c r="R12">
-        <v>4</v>
-      </c>
-      <c r="T12" t="s">
-        <v>107</v>
-      </c>
-      <c r="U12" s="4">
-        <v>45397</v>
-      </c>
-      <c r="V12" s="4">
-        <v>46127</v>
-      </c>
-      <c r="W12" t="s">
-        <v>34</v>
-      </c>
-      <c r="X12">
-        <v>160</v>
-      </c>
-      <c r="Y12" s="4">
-        <v>45717</v>
-      </c>
-      <c r="Z12">
-        <v>18</v>
-      </c>
-      <c r="AA12">
-        <v>450</v>
-      </c>
-      <c r="AB12">
-        <v>8</v>
-      </c>
-      <c r="AC12">
-        <v>25</v>
-      </c>
-      <c r="AD12">
-        <v>5</v>
-      </c>
-      <c r="AE12">
-        <f t="shared" si="1"/>
-        <v>389</v>
-      </c>
-      <c r="AF12">
-        <v>5</v>
-      </c>
-      <c r="AG12">
-        <v>30029099</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+        <v/>
+      </c>
+      <c r="AE12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:33">
       <c r="P13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1978,7 +951,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33">
       <c r="P14" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1988,7 +961,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33">
       <c r="P15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1998,7 +971,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33">
       <c r="P16" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2008,7 +981,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="17" spans="16:31">
       <c r="P17" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2018,7 +991,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="18" spans="16:31">
       <c r="P18" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2028,7 +1001,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="19" spans="16:31">
       <c r="P19" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2038,7 +1011,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="20" spans="16:31">
       <c r="P20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2048,7 +1021,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="21" spans="16:31">
       <c r="P21" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2058,7 +1031,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="22" spans="16:31">
       <c r="P22" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2068,7 +1041,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="23" spans="16:31">
       <c r="P23" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2078,7 +1051,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="24" spans="16:31">
       <c r="P24" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2088,7 +1061,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="25" spans="16:31">
       <c r="P25" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2098,7 +1071,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="26" spans="16:31">
       <c r="P26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2108,7 +1081,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="27" spans="16:31">
       <c r="P27" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2118,7 +1091,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="28" spans="16:31">
       <c r="P28" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2128,7 +1101,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="29" spans="16:31">
       <c r="P29" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2138,7 +1111,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="30" spans="16:31">
       <c r="P30" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2148,7 +1121,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="31" spans="16:31">
       <c r="P31" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2158,7 +1131,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="32" spans="16:31">
       <c r="P32" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2168,7 +1141,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="33" spans="16:31">
       <c r="P33" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2178,7 +1151,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="34" spans="16:31">
       <c r="P34" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2188,7 +1161,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="35" spans="16:31">
       <c r="P35" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2198,7 +1171,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="36" spans="16:31">
       <c r="P36" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2208,7 +1181,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="37" spans="16:31">
       <c r="P37" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2218,7 +1191,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="38" spans="16:31">
       <c r="P38" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2228,7 +1201,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="39" spans="16:31">
       <c r="P39" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2238,7 +1211,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="40" spans="16:31">
       <c r="P40" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2248,7 +1221,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="41" spans="16:31">
       <c r="P41" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2258,7 +1231,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="42" spans="16:31">
       <c r="P42" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2268,7 +1241,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="43" spans="16:31">
       <c r="P43" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2278,7 +1251,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="44" spans="16:31">
       <c r="P44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2288,7 +1261,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="45" spans="16:31">
       <c r="P45" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2298,7 +1271,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="46" spans="16:31">
       <c r="P46" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2308,7 +1281,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="47" spans="16:31">
       <c r="P47" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2318,7 +1291,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="48" spans="16:31">
       <c r="P48" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2328,7 +1301,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="49" spans="16:31">
       <c r="P49" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2338,7 +1311,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="50" spans="16:31">
       <c r="P50" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2348,7 +1321,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="51" spans="16:31">
       <c r="P51" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2358,7 +1331,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="52" spans="16:31">
       <c r="P52" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2368,7 +1341,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="53" spans="16:31">
       <c r="P53" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2378,7 +1351,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="54" spans="16:31">
       <c r="P54" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2388,7 +1361,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="55" spans="16:31">
       <c r="P55" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2398,7 +1371,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="56" spans="16:31">
       <c r="P56" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2408,7 +1381,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="57" spans="16:31">
       <c r="P57" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2418,7 +1391,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="58" spans="16:31">
       <c r="P58" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2428,7 +1401,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="59" spans="16:31">
       <c r="P59" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2438,7 +1411,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="60" spans="16:31">
       <c r="P60" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2448,7 +1421,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="61" spans="16:31">
       <c r="P61" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2458,7 +1431,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="62" spans="16:31">
       <c r="P62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2468,7 +1441,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="63" spans="16:31">
       <c r="P63" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2478,7 +1451,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="64" spans="16:31">
       <c r="P64" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2488,7 +1461,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="65" spans="16:31">
       <c r="P65" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2498,7 +1471,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="66" spans="16:31">
       <c r="P66" t="str">
         <f t="shared" ref="P66:P129" si="2">IF(AND(N66&lt;&gt;"",O66&lt;&gt;""),N66&amp;" x "&amp;O66,"")</f>
         <v/>
@@ -2508,7 +1481,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="67" spans="16:31">
       <c r="P67" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2518,7 +1491,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="68" spans="16:31">
       <c r="P68" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2528,7 +1501,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="69" spans="16:31">
       <c r="P69" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2538,7 +1511,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="70" spans="16:31">
       <c r="P70" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2548,7 +1521,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="71" spans="16:31">
       <c r="P71" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2558,7 +1531,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="72" spans="16:31">
       <c r="P72" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2568,7 +1541,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="73" spans="16:31">
       <c r="P73" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2578,7 +1551,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="74" spans="16:31">
       <c r="P74" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2588,7 +1561,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="75" spans="16:31">
       <c r="P75" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2598,7 +1571,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="76" spans="16:31">
       <c r="P76" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2608,7 +1581,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="77" spans="16:31">
       <c r="P77" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2618,7 +1591,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="78" spans="16:31">
       <c r="P78" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2628,7 +1601,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="79" spans="16:31">
       <c r="P79" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2638,7 +1611,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="80" spans="16:31">
       <c r="P80" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2648,7 +1621,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="81" spans="16:31">
       <c r="P81" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2658,7 +1631,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="82" spans="16:31">
       <c r="P82" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2668,7 +1641,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="83" spans="16:31">
       <c r="P83" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2678,7 +1651,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="84" spans="16:31">
       <c r="P84" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2688,7 +1661,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="85" spans="16:31">
       <c r="P85" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2698,7 +1671,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="86" spans="16:31">
       <c r="P86" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2708,7 +1681,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="87" spans="16:31">
       <c r="P87" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2718,7 +1691,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="88" spans="16:31">
       <c r="P88" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2728,7 +1701,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="89" spans="16:31">
       <c r="P89" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2738,7 +1711,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="90" spans="16:31">
       <c r="P90" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2748,7 +1721,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="91" spans="16:31">
       <c r="P91" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2758,7 +1731,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="92" spans="16:31">
       <c r="P92" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2768,7 +1741,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="93" spans="16:31">
       <c r="P93" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2778,7 +1751,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="94" spans="16:31">
       <c r="P94" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2788,7 +1761,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="95" spans="16:31">
       <c r="P95" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2798,7 +1771,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="96" spans="16:31">
       <c r="P96" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2808,7 +1781,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="97" spans="16:31">
       <c r="P97" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2818,7 +1791,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="98" spans="16:31">
       <c r="P98" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2828,7 +1801,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="99" spans="16:31">
       <c r="P99" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2838,7 +1811,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="100" spans="16:31">
       <c r="P100" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2848,7 +1821,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="101" spans="16:31">
       <c r="P101" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2858,7 +1831,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="102" spans="16:31">
       <c r="P102" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2868,7 +1841,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="103" spans="16:31">
       <c r="P103" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2878,7 +1851,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="104" spans="16:31">
       <c r="P104" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2888,7 +1861,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="105" spans="16:31">
       <c r="P105" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2898,7 +1871,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="106" spans="16:31">
       <c r="P106" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2908,7 +1881,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="107" spans="16:31">
       <c r="P107" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2918,7 +1891,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="108" spans="16:31">
       <c r="P108" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2928,7 +1901,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="109" spans="16:31">
       <c r="P109" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2938,7 +1911,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="110" spans="16:31">
       <c r="P110" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2948,7 +1921,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="111" spans="16:31">
       <c r="P111" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2958,7 +1931,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="112" spans="16:31">
       <c r="P112" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2968,7 +1941,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="113" spans="16:31">
       <c r="P113" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2978,7 +1951,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="114" spans="16:31">
       <c r="P114" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2988,7 +1961,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="115" spans="16:31">
       <c r="P115" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2998,7 +1971,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="116" spans="16:31">
       <c r="P116" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3008,7 +1981,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="117" spans="16:31">
       <c r="P117" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3018,7 +1991,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="118" spans="16:31">
       <c r="P118" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3028,7 +2001,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="119" spans="16:31">
       <c r="P119" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3038,7 +2011,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="120" spans="16:31">
       <c r="P120" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3048,7 +2021,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="121" spans="16:31">
       <c r="P121" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3058,7 +2031,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="122" spans="16:31">
       <c r="P122" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3068,7 +2041,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="123" spans="16:31">
       <c r="P123" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3078,7 +2051,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="124" spans="16:31">
       <c r="P124" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3088,7 +2061,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="125" spans="16:31">
       <c r="P125" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3098,7 +2071,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="126" spans="16:31">
       <c r="P126" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3108,7 +2081,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="127" spans="16:31">
       <c r="P127" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3118,7 +2091,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="128" spans="16:31">
       <c r="P128" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3128,7 +2101,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="129" spans="16:31">
       <c r="P129" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3138,7 +2111,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="130" spans="16:31">
       <c r="P130" t="str">
         <f t="shared" ref="P130:P193" si="4">IF(AND(N130&lt;&gt;"",O130&lt;&gt;""),N130&amp;" x "&amp;O130,"")</f>
         <v/>
@@ -3148,7 +2121,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="131" spans="16:31">
       <c r="P131" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3158,7 +2131,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="132" spans="16:31">
       <c r="P132" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3168,7 +2141,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="133" spans="16:31">
       <c r="P133" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3178,7 +2151,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="134" spans="16:31">
       <c r="P134" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3188,7 +2161,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="135" spans="16:31">
       <c r="P135" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3198,7 +2171,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="136" spans="16:31">
       <c r="P136" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3208,7 +2181,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="137" spans="16:31">
       <c r="P137" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3218,7 +2191,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="138" spans="16:31">
       <c r="P138" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3228,7 +2201,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="139" spans="16:31">
       <c r="P139" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3238,7 +2211,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="140" spans="16:31">
       <c r="P140" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3248,7 +2221,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="141" spans="16:31">
       <c r="P141" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3258,7 +2231,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="142" spans="16:31">
       <c r="P142" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3268,7 +2241,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="143" spans="16:31">
       <c r="P143" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3278,7 +2251,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="144" spans="16:31">
       <c r="P144" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3288,7 +2261,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="145" spans="16:31">
       <c r="P145" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3298,7 +2271,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="146" spans="16:31">
       <c r="P146" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3308,7 +2281,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="147" spans="16:31">
       <c r="P147" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3318,7 +2291,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="148" spans="16:31">
       <c r="P148" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3328,7 +2301,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="149" spans="16:31">
       <c r="P149" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3338,7 +2311,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="150" spans="16:31">
       <c r="P150" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3348,7 +2321,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="151" spans="16:31">
       <c r="P151" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3358,7 +2331,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="152" spans="16:31">
       <c r="P152" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3368,7 +2341,7 @@
         <v/>
       </c>
     </row>
-    <row r="153" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="153" spans="16:31">
       <c r="P153" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3378,7 +2351,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="154" spans="16:31">
       <c r="P154" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3388,7 +2361,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="155" spans="16:31">
       <c r="P155" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3398,7 +2371,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="156" spans="16:31">
       <c r="P156" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3408,7 +2381,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="157" spans="16:31">
       <c r="P157" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3418,7 +2391,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="158" spans="16:31">
       <c r="P158" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3428,7 +2401,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="159" spans="16:31">
       <c r="P159" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3438,7 +2411,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="160" spans="16:31">
       <c r="P160" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3448,7 +2421,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="161" spans="16:31">
       <c r="P161" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3458,7 +2431,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="162" spans="16:31">
       <c r="P162" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3468,7 +2441,7 @@
         <v/>
       </c>
     </row>
-    <row r="163" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="163" spans="16:31">
       <c r="P163" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3478,7 +2451,7 @@
         <v/>
       </c>
     </row>
-    <row r="164" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="164" spans="16:31">
       <c r="P164" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3488,7 +2461,7 @@
         <v/>
       </c>
     </row>
-    <row r="165" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="165" spans="16:31">
       <c r="P165" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3498,7 +2471,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="166" spans="16:31">
       <c r="P166" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3508,7 +2481,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="167" spans="16:31">
       <c r="P167" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3518,7 +2491,7 @@
         <v/>
       </c>
     </row>
-    <row r="168" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="168" spans="16:31">
       <c r="P168" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3528,7 +2501,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="169" spans="16:31">
       <c r="P169" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3538,7 +2511,7 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="170" spans="16:31">
       <c r="P170" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3548,7 +2521,7 @@
         <v/>
       </c>
     </row>
-    <row r="171" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="171" spans="16:31">
       <c r="P171" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3558,7 +2531,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="172" spans="16:31">
       <c r="P172" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3568,7 +2541,7 @@
         <v/>
       </c>
     </row>
-    <row r="173" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="173" spans="16:31">
       <c r="P173" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3578,7 +2551,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="174" spans="16:31">
       <c r="P174" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3588,7 +2561,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="175" spans="16:31">
       <c r="P175" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3598,7 +2571,7 @@
         <v/>
       </c>
     </row>
-    <row r="176" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="176" spans="16:31">
       <c r="P176" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3608,7 +2581,7 @@
         <v/>
       </c>
     </row>
-    <row r="177" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="177" spans="16:31">
       <c r="P177" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3618,7 +2591,7 @@
         <v/>
       </c>
     </row>
-    <row r="178" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="178" spans="16:31">
       <c r="P178" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3628,7 +2601,7 @@
         <v/>
       </c>
     </row>
-    <row r="179" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="179" spans="16:31">
       <c r="P179" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3638,7 +2611,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="180" spans="16:31">
       <c r="P180" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3648,7 +2621,7 @@
         <v/>
       </c>
     </row>
-    <row r="181" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="181" spans="16:31">
       <c r="P181" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3658,7 +2631,7 @@
         <v/>
       </c>
     </row>
-    <row r="182" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="182" spans="16:31">
       <c r="P182" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3668,7 +2641,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="183" spans="16:31">
       <c r="P183" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3678,7 +2651,7 @@
         <v/>
       </c>
     </row>
-    <row r="184" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="184" spans="16:31">
       <c r="P184" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3688,7 +2661,7 @@
         <v/>
       </c>
     </row>
-    <row r="185" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="185" spans="16:31">
       <c r="P185" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3698,7 +2671,7 @@
         <v/>
       </c>
     </row>
-    <row r="186" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="186" spans="16:31">
       <c r="P186" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3708,7 +2681,7 @@
         <v/>
       </c>
     </row>
-    <row r="187" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="187" spans="16:31">
       <c r="P187" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3718,7 +2691,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="188" spans="16:31">
       <c r="P188" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3728,7 +2701,7 @@
         <v/>
       </c>
     </row>
-    <row r="189" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="189" spans="16:31">
       <c r="P189" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3738,7 +2711,7 @@
         <v/>
       </c>
     </row>
-    <row r="190" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="190" spans="16:31">
       <c r="P190" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3748,7 +2721,7 @@
         <v/>
       </c>
     </row>
-    <row r="191" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="191" spans="16:31">
       <c r="P191" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3758,7 +2731,7 @@
         <v/>
       </c>
     </row>
-    <row r="192" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="192" spans="16:31">
       <c r="P192" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3768,7 +2741,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="193" spans="16:31">
       <c r="P193" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3778,7 +2751,7 @@
         <v/>
       </c>
     </row>
-    <row r="194" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="194" spans="16:31">
       <c r="P194" t="str">
         <f t="shared" ref="P194:P257" si="6">IF(AND(N194&lt;&gt;"",O194&lt;&gt;""),N194&amp;" x "&amp;O194,"")</f>
         <v/>
@@ -3788,7 +2761,7 @@
         <v/>
       </c>
     </row>
-    <row r="195" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="195" spans="16:31">
       <c r="P195" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3798,7 +2771,7 @@
         <v/>
       </c>
     </row>
-    <row r="196" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="196" spans="16:31">
       <c r="P196" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3808,7 +2781,7 @@
         <v/>
       </c>
     </row>
-    <row r="197" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="197" spans="16:31">
       <c r="P197" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3818,7 +2791,7 @@
         <v/>
       </c>
     </row>
-    <row r="198" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="198" spans="16:31">
       <c r="P198" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3828,7 +2801,7 @@
         <v/>
       </c>
     </row>
-    <row r="199" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="199" spans="16:31">
       <c r="P199" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3838,7 +2811,7 @@
         <v/>
       </c>
     </row>
-    <row r="200" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="200" spans="16:31">
       <c r="P200" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3848,7 +2821,7 @@
         <v/>
       </c>
     </row>
-    <row r="201" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="201" spans="16:31">
       <c r="P201" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3858,7 +2831,7 @@
         <v/>
       </c>
     </row>
-    <row r="202" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="202" spans="16:31">
       <c r="P202" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3868,7 +2841,7 @@
         <v/>
       </c>
     </row>
-    <row r="203" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="203" spans="16:31">
       <c r="P203" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3878,7 +2851,7 @@
         <v/>
       </c>
     </row>
-    <row r="204" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="204" spans="16:31">
       <c r="P204" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3888,7 +2861,7 @@
         <v/>
       </c>
     </row>
-    <row r="205" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="205" spans="16:31">
       <c r="P205" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3898,7 +2871,7 @@
         <v/>
       </c>
     </row>
-    <row r="206" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="206" spans="16:31">
       <c r="P206" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3908,7 +2881,7 @@
         <v/>
       </c>
     </row>
-    <row r="207" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="207" spans="16:31">
       <c r="P207" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3918,7 +2891,7 @@
         <v/>
       </c>
     </row>
-    <row r="208" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="208" spans="16:31">
       <c r="P208" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3928,7 +2901,7 @@
         <v/>
       </c>
     </row>
-    <row r="209" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="209" spans="16:31">
       <c r="P209" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3938,7 +2911,7 @@
         <v/>
       </c>
     </row>
-    <row r="210" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="210" spans="16:31">
       <c r="P210" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3948,7 +2921,7 @@
         <v/>
       </c>
     </row>
-    <row r="211" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="211" spans="16:31">
       <c r="P211" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3958,7 +2931,7 @@
         <v/>
       </c>
     </row>
-    <row r="212" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="212" spans="16:31">
       <c r="P212" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3968,7 +2941,7 @@
         <v/>
       </c>
     </row>
-    <row r="213" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="213" spans="16:31">
       <c r="P213" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3978,7 +2951,7 @@
         <v/>
       </c>
     </row>
-    <row r="214" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="214" spans="16:31">
       <c r="P214" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3988,7 +2961,7 @@
         <v/>
       </c>
     </row>
-    <row r="215" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="215" spans="16:31">
       <c r="P215" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3998,7 +2971,7 @@
         <v/>
       </c>
     </row>
-    <row r="216" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="216" spans="16:31">
       <c r="P216" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4008,7 +2981,7 @@
         <v/>
       </c>
     </row>
-    <row r="217" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="217" spans="16:31">
       <c r="P217" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4018,7 +2991,7 @@
         <v/>
       </c>
     </row>
-    <row r="218" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="218" spans="16:31">
       <c r="P218" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4028,7 +3001,7 @@
         <v/>
       </c>
     </row>
-    <row r="219" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="219" spans="16:31">
       <c r="P219" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4038,7 +3011,7 @@
         <v/>
       </c>
     </row>
-    <row r="220" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="220" spans="16:31">
       <c r="P220" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4048,7 +3021,7 @@
         <v/>
       </c>
     </row>
-    <row r="221" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="221" spans="16:31">
       <c r="P221" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4058,7 +3031,7 @@
         <v/>
       </c>
     </row>
-    <row r="222" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="222" spans="16:31">
       <c r="P222" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4068,7 +3041,7 @@
         <v/>
       </c>
     </row>
-    <row r="223" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="223" spans="16:31">
       <c r="P223" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4078,7 +3051,7 @@
         <v/>
       </c>
     </row>
-    <row r="224" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="224" spans="16:31">
       <c r="P224" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4088,7 +3061,7 @@
         <v/>
       </c>
     </row>
-    <row r="225" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="225" spans="16:31">
       <c r="P225" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4098,7 +3071,7 @@
         <v/>
       </c>
     </row>
-    <row r="226" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="226" spans="16:31">
       <c r="P226" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4108,7 +3081,7 @@
         <v/>
       </c>
     </row>
-    <row r="227" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="227" spans="16:31">
       <c r="P227" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4118,7 +3091,7 @@
         <v/>
       </c>
     </row>
-    <row r="228" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="228" spans="16:31">
       <c r="P228" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4128,7 +3101,7 @@
         <v/>
       </c>
     </row>
-    <row r="229" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="229" spans="16:31">
       <c r="P229" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4138,7 +3111,7 @@
         <v/>
       </c>
     </row>
-    <row r="230" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="230" spans="16:31">
       <c r="P230" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4148,7 +3121,7 @@
         <v/>
       </c>
     </row>
-    <row r="231" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="231" spans="16:31">
       <c r="P231" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4158,7 +3131,7 @@
         <v/>
       </c>
     </row>
-    <row r="232" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="232" spans="16:31">
       <c r="P232" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4168,7 +3141,7 @@
         <v/>
       </c>
     </row>
-    <row r="233" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="233" spans="16:31">
       <c r="P233" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4178,7 +3151,7 @@
         <v/>
       </c>
     </row>
-    <row r="234" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="234" spans="16:31">
       <c r="P234" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4188,7 +3161,7 @@
         <v/>
       </c>
     </row>
-    <row r="235" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="235" spans="16:31">
       <c r="P235" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4198,7 +3171,7 @@
         <v/>
       </c>
     </row>
-    <row r="236" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="236" spans="16:31">
       <c r="P236" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4208,7 +3181,7 @@
         <v/>
       </c>
     </row>
-    <row r="237" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="237" spans="16:31">
       <c r="P237" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4218,7 +3191,7 @@
         <v/>
       </c>
     </row>
-    <row r="238" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="238" spans="16:31">
       <c r="P238" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4228,7 +3201,7 @@
         <v/>
       </c>
     </row>
-    <row r="239" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="239" spans="16:31">
       <c r="P239" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4238,7 +3211,7 @@
         <v/>
       </c>
     </row>
-    <row r="240" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="240" spans="16:31">
       <c r="P240" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4248,7 +3221,7 @@
         <v/>
       </c>
     </row>
-    <row r="241" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="241" spans="16:31">
       <c r="P241" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4258,7 +3231,7 @@
         <v/>
       </c>
     </row>
-    <row r="242" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="242" spans="16:31">
       <c r="P242" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4268,7 +3241,7 @@
         <v/>
       </c>
     </row>
-    <row r="243" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="243" spans="16:31">
       <c r="P243" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4278,7 +3251,7 @@
         <v/>
       </c>
     </row>
-    <row r="244" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="244" spans="16:31">
       <c r="P244" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4288,7 +3261,7 @@
         <v/>
       </c>
     </row>
-    <row r="245" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="245" spans="16:31">
       <c r="P245" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4298,7 +3271,7 @@
         <v/>
       </c>
     </row>
-    <row r="246" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="246" spans="16:31">
       <c r="P246" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4308,7 +3281,7 @@
         <v/>
       </c>
     </row>
-    <row r="247" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="247" spans="16:31">
       <c r="P247" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4318,7 +3291,7 @@
         <v/>
       </c>
     </row>
-    <row r="248" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="248" spans="16:31">
       <c r="P248" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4328,7 +3301,7 @@
         <v/>
       </c>
     </row>
-    <row r="249" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="249" spans="16:31">
       <c r="P249" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4338,7 +3311,7 @@
         <v/>
       </c>
     </row>
-    <row r="250" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="250" spans="16:31">
       <c r="P250" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4348,7 +3321,7 @@
         <v/>
       </c>
     </row>
-    <row r="251" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="251" spans="16:31">
       <c r="P251" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4358,7 +3331,7 @@
         <v/>
       </c>
     </row>
-    <row r="252" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="252" spans="16:31">
       <c r="P252" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4368,7 +3341,7 @@
         <v/>
       </c>
     </row>
-    <row r="253" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="253" spans="16:31">
       <c r="P253" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4378,7 +3351,7 @@
         <v/>
       </c>
     </row>
-    <row r="254" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="254" spans="16:31">
       <c r="P254" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4388,7 +3361,7 @@
         <v/>
       </c>
     </row>
-    <row r="255" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="255" spans="16:31">
       <c r="P255" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4398,7 +3371,7 @@
         <v/>
       </c>
     </row>
-    <row r="256" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="256" spans="16:31">
       <c r="P256" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4408,7 +3381,7 @@
         <v/>
       </c>
     </row>
-    <row r="257" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="257" spans="16:31">
       <c r="P257" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4418,7 +3391,7 @@
         <v/>
       </c>
     </row>
-    <row r="258" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="258" spans="16:31">
       <c r="P258" t="str">
         <f t="shared" ref="P258:P321" si="8">IF(AND(N258&lt;&gt;"",O258&lt;&gt;""),N258&amp;" x "&amp;O258,"")</f>
         <v/>
@@ -4428,7 +3401,7 @@
         <v/>
       </c>
     </row>
-    <row r="259" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="259" spans="16:31">
       <c r="P259" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4438,7 +3411,7 @@
         <v/>
       </c>
     </row>
-    <row r="260" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="260" spans="16:31">
       <c r="P260" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4448,7 +3421,7 @@
         <v/>
       </c>
     </row>
-    <row r="261" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="261" spans="16:31">
       <c r="P261" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4458,7 +3431,7 @@
         <v/>
       </c>
     </row>
-    <row r="262" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="262" spans="16:31">
       <c r="P262" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4468,7 +3441,7 @@
         <v/>
       </c>
     </row>
-    <row r="263" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="263" spans="16:31">
       <c r="P263" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4478,7 +3451,7 @@
         <v/>
       </c>
     </row>
-    <row r="264" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="264" spans="16:31">
       <c r="P264" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4488,7 +3461,7 @@
         <v/>
       </c>
     </row>
-    <row r="265" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="265" spans="16:31">
       <c r="P265" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4498,7 +3471,7 @@
         <v/>
       </c>
     </row>
-    <row r="266" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="266" spans="16:31">
       <c r="P266" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4508,7 +3481,7 @@
         <v/>
       </c>
     </row>
-    <row r="267" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="267" spans="16:31">
       <c r="P267" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4518,7 +3491,7 @@
         <v/>
       </c>
     </row>
-    <row r="268" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="268" spans="16:31">
       <c r="P268" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4528,7 +3501,7 @@
         <v/>
       </c>
     </row>
-    <row r="269" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="269" spans="16:31">
       <c r="P269" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4538,7 +3511,7 @@
         <v/>
       </c>
     </row>
-    <row r="270" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="270" spans="16:31">
       <c r="P270" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4548,7 +3521,7 @@
         <v/>
       </c>
     </row>
-    <row r="271" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="271" spans="16:31">
       <c r="P271" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4558,7 +3531,7 @@
         <v/>
       </c>
     </row>
-    <row r="272" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="272" spans="16:31">
       <c r="P272" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4568,7 +3541,7 @@
         <v/>
       </c>
     </row>
-    <row r="273" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="273" spans="16:31">
       <c r="P273" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4578,7 +3551,7 @@
         <v/>
       </c>
     </row>
-    <row r="274" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="274" spans="16:31">
       <c r="P274" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4588,7 +3561,7 @@
         <v/>
       </c>
     </row>
-    <row r="275" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="275" spans="16:31">
       <c r="P275" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4598,7 +3571,7 @@
         <v/>
       </c>
     </row>
-    <row r="276" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="276" spans="16:31">
       <c r="P276" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4608,7 +3581,7 @@
         <v/>
       </c>
     </row>
-    <row r="277" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="277" spans="16:31">
       <c r="P277" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4618,7 +3591,7 @@
         <v/>
       </c>
     </row>
-    <row r="278" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="278" spans="16:31">
       <c r="P278" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4628,7 +3601,7 @@
         <v/>
       </c>
     </row>
-    <row r="279" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="279" spans="16:31">
       <c r="P279" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4638,7 +3611,7 @@
         <v/>
       </c>
     </row>
-    <row r="280" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="280" spans="16:31">
       <c r="P280" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4648,7 +3621,7 @@
         <v/>
       </c>
     </row>
-    <row r="281" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="281" spans="16:31">
       <c r="P281" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4658,7 +3631,7 @@
         <v/>
       </c>
     </row>
-    <row r="282" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="282" spans="16:31">
       <c r="P282" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4668,7 +3641,7 @@
         <v/>
       </c>
     </row>
-    <row r="283" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="283" spans="16:31">
       <c r="P283" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4678,7 +3651,7 @@
         <v/>
       </c>
     </row>
-    <row r="284" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="284" spans="16:31">
       <c r="P284" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4688,7 +3661,7 @@
         <v/>
       </c>
     </row>
-    <row r="285" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="285" spans="16:31">
       <c r="P285" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4698,7 +3671,7 @@
         <v/>
       </c>
     </row>
-    <row r="286" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="286" spans="16:31">
       <c r="P286" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4708,7 +3681,7 @@
         <v/>
       </c>
     </row>
-    <row r="287" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="287" spans="16:31">
       <c r="P287" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4718,7 +3691,7 @@
         <v/>
       </c>
     </row>
-    <row r="288" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="288" spans="16:31">
       <c r="P288" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4728,7 +3701,7 @@
         <v/>
       </c>
     </row>
-    <row r="289" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="289" spans="16:31">
       <c r="P289" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4738,7 +3711,7 @@
         <v/>
       </c>
     </row>
-    <row r="290" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="290" spans="16:31">
       <c r="P290" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4748,7 +3721,7 @@
         <v/>
       </c>
     </row>
-    <row r="291" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="291" spans="16:31">
       <c r="P291" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4758,7 +3731,7 @@
         <v/>
       </c>
     </row>
-    <row r="292" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="292" spans="16:31">
       <c r="P292" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4768,7 +3741,7 @@
         <v/>
       </c>
     </row>
-    <row r="293" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="293" spans="16:31">
       <c r="P293" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4778,7 +3751,7 @@
         <v/>
       </c>
     </row>
-    <row r="294" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="294" spans="16:31">
       <c r="P294" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4788,7 +3761,7 @@
         <v/>
       </c>
     </row>
-    <row r="295" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="295" spans="16:31">
       <c r="P295" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4798,7 +3771,7 @@
         <v/>
       </c>
     </row>
-    <row r="296" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="296" spans="16:31">
       <c r="P296" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4808,7 +3781,7 @@
         <v/>
       </c>
     </row>
-    <row r="297" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="297" spans="16:31">
       <c r="P297" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4818,7 +3791,7 @@
         <v/>
       </c>
     </row>
-    <row r="298" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="298" spans="16:31">
       <c r="P298" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4828,7 +3801,7 @@
         <v/>
       </c>
     </row>
-    <row r="299" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="299" spans="16:31">
       <c r="P299" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4838,7 +3811,7 @@
         <v/>
       </c>
     </row>
-    <row r="300" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="300" spans="16:31">
       <c r="P300" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4848,7 +3821,7 @@
         <v/>
       </c>
     </row>
-    <row r="301" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="301" spans="16:31">
       <c r="P301" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4858,7 +3831,7 @@
         <v/>
       </c>
     </row>
-    <row r="302" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="302" spans="16:31">
       <c r="P302" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4868,7 +3841,7 @@
         <v/>
       </c>
     </row>
-    <row r="303" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="303" spans="16:31">
       <c r="P303" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4878,7 +3851,7 @@
         <v/>
       </c>
     </row>
-    <row r="304" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="304" spans="16:31">
       <c r="P304" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4888,7 +3861,7 @@
         <v/>
       </c>
     </row>
-    <row r="305" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="305" spans="16:31">
       <c r="P305" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4898,7 +3871,7 @@
         <v/>
       </c>
     </row>
-    <row r="306" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="306" spans="16:31">
       <c r="P306" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4908,7 +3881,7 @@
         <v/>
       </c>
     </row>
-    <row r="307" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="307" spans="16:31">
       <c r="P307" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4918,7 +3891,7 @@
         <v/>
       </c>
     </row>
-    <row r="308" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="308" spans="16:31">
       <c r="P308" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4928,7 +3901,7 @@
         <v/>
       </c>
     </row>
-    <row r="309" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="309" spans="16:31">
       <c r="P309" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4938,7 +3911,7 @@
         <v/>
       </c>
     </row>
-    <row r="310" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="310" spans="16:31">
       <c r="P310" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4948,7 +3921,7 @@
         <v/>
       </c>
     </row>
-    <row r="311" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="311" spans="16:31">
       <c r="P311" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4958,7 +3931,7 @@
         <v/>
       </c>
     </row>
-    <row r="312" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="312" spans="16:31">
       <c r="P312" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4968,7 +3941,7 @@
         <v/>
       </c>
     </row>
-    <row r="313" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="313" spans="16:31">
       <c r="P313" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4978,7 +3951,7 @@
         <v/>
       </c>
     </row>
-    <row r="314" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="314" spans="16:31">
       <c r="P314" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4988,7 +3961,7 @@
         <v/>
       </c>
     </row>
-    <row r="315" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="315" spans="16:31">
       <c r="P315" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4998,7 +3971,7 @@
         <v/>
       </c>
     </row>
-    <row r="316" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="316" spans="16:31">
       <c r="P316" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5008,7 +3981,7 @@
         <v/>
       </c>
     </row>
-    <row r="317" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="317" spans="16:31">
       <c r="P317" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5018,7 +3991,7 @@
         <v/>
       </c>
     </row>
-    <row r="318" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="318" spans="16:31">
       <c r="P318" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5028,7 +4001,7 @@
         <v/>
       </c>
     </row>
-    <row r="319" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="319" spans="16:31">
       <c r="P319" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5038,7 +4011,7 @@
         <v/>
       </c>
     </row>
-    <row r="320" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="320" spans="16:31">
       <c r="P320" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5048,7 +4021,7 @@
         <v/>
       </c>
     </row>
-    <row r="321" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="321" spans="16:31">
       <c r="P321" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5058,7 +4031,7 @@
         <v/>
       </c>
     </row>
-    <row r="322" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="322" spans="16:31">
       <c r="P322" t="str">
         <f t="shared" ref="P322:P385" si="10">IF(AND(N322&lt;&gt;"",O322&lt;&gt;""),N322&amp;" x "&amp;O322,"")</f>
         <v/>
@@ -5068,7 +4041,7 @@
         <v/>
       </c>
     </row>
-    <row r="323" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="323" spans="16:31">
       <c r="P323" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5078,7 +4051,7 @@
         <v/>
       </c>
     </row>
-    <row r="324" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="324" spans="16:31">
       <c r="P324" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5088,7 +4061,7 @@
         <v/>
       </c>
     </row>
-    <row r="325" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="325" spans="16:31">
       <c r="P325" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5098,7 +4071,7 @@
         <v/>
       </c>
     </row>
-    <row r="326" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="326" spans="16:31">
       <c r="P326" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5108,7 +4081,7 @@
         <v/>
       </c>
     </row>
-    <row r="327" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="327" spans="16:31">
       <c r="P327" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5118,7 +4091,7 @@
         <v/>
       </c>
     </row>
-    <row r="328" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="328" spans="16:31">
       <c r="P328" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5128,7 +4101,7 @@
         <v/>
       </c>
     </row>
-    <row r="329" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="329" spans="16:31">
       <c r="P329" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5138,7 +4111,7 @@
         <v/>
       </c>
     </row>
-    <row r="330" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="330" spans="16:31">
       <c r="P330" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5148,7 +4121,7 @@
         <v/>
       </c>
     </row>
-    <row r="331" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="331" spans="16:31">
       <c r="P331" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5158,7 +4131,7 @@
         <v/>
       </c>
     </row>
-    <row r="332" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="332" spans="16:31">
       <c r="P332" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5168,7 +4141,7 @@
         <v/>
       </c>
     </row>
-    <row r="333" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="333" spans="16:31">
       <c r="P333" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5178,7 +4151,7 @@
         <v/>
       </c>
     </row>
-    <row r="334" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="334" spans="16:31">
       <c r="P334" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5188,7 +4161,7 @@
         <v/>
       </c>
     </row>
-    <row r="335" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="335" spans="16:31">
       <c r="P335" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5198,7 +4171,7 @@
         <v/>
       </c>
     </row>
-    <row r="336" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="336" spans="16:31">
       <c r="P336" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5208,7 +4181,7 @@
         <v/>
       </c>
     </row>
-    <row r="337" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="337" spans="16:31">
       <c r="P337" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5218,7 +4191,7 @@
         <v/>
       </c>
     </row>
-    <row r="338" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="338" spans="16:31">
       <c r="P338" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5228,7 +4201,7 @@
         <v/>
       </c>
     </row>
-    <row r="339" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="339" spans="16:31">
       <c r="P339" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5238,7 +4211,7 @@
         <v/>
       </c>
     </row>
-    <row r="340" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="340" spans="16:31">
       <c r="P340" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5248,7 +4221,7 @@
         <v/>
       </c>
     </row>
-    <row r="341" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="341" spans="16:31">
       <c r="P341" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5258,7 +4231,7 @@
         <v/>
       </c>
     </row>
-    <row r="342" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="342" spans="16:31">
       <c r="P342" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5268,7 +4241,7 @@
         <v/>
       </c>
     </row>
-    <row r="343" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="343" spans="16:31">
       <c r="P343" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5278,7 +4251,7 @@
         <v/>
       </c>
     </row>
-    <row r="344" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="344" spans="16:31">
       <c r="P344" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5288,7 +4261,7 @@
         <v/>
       </c>
     </row>
-    <row r="345" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="345" spans="16:31">
       <c r="P345" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5298,7 +4271,7 @@
         <v/>
       </c>
     </row>
-    <row r="346" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="346" spans="16:31">
       <c r="P346" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5308,7 +4281,7 @@
         <v/>
       </c>
     </row>
-    <row r="347" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="347" spans="16:31">
       <c r="P347" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5318,7 +4291,7 @@
         <v/>
       </c>
     </row>
-    <row r="348" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="348" spans="16:31">
       <c r="P348" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5328,7 +4301,7 @@
         <v/>
       </c>
     </row>
-    <row r="349" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="349" spans="16:31">
       <c r="P349" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5338,7 +4311,7 @@
         <v/>
       </c>
     </row>
-    <row r="350" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="350" spans="16:31">
       <c r="P350" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5348,7 +4321,7 @@
         <v/>
       </c>
     </row>
-    <row r="351" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="351" spans="16:31">
       <c r="P351" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5358,7 +4331,7 @@
         <v/>
       </c>
     </row>
-    <row r="352" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="352" spans="16:31">
       <c r="P352" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5368,7 +4341,7 @@
         <v/>
       </c>
     </row>
-    <row r="353" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="353" spans="16:31">
       <c r="P353" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5378,7 +4351,7 @@
         <v/>
       </c>
     </row>
-    <row r="354" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="354" spans="16:31">
       <c r="P354" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5388,7 +4361,7 @@
         <v/>
       </c>
     </row>
-    <row r="355" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="355" spans="16:31">
       <c r="P355" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5398,7 +4371,7 @@
         <v/>
       </c>
     </row>
-    <row r="356" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="356" spans="16:31">
       <c r="P356" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5408,7 +4381,7 @@
         <v/>
       </c>
     </row>
-    <row r="357" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="357" spans="16:31">
       <c r="P357" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5418,7 +4391,7 @@
         <v/>
       </c>
     </row>
-    <row r="358" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="358" spans="16:31">
       <c r="P358" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5428,7 +4401,7 @@
         <v/>
       </c>
     </row>
-    <row r="359" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="359" spans="16:31">
       <c r="P359" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5438,7 +4411,7 @@
         <v/>
       </c>
     </row>
-    <row r="360" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="360" spans="16:31">
       <c r="P360" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5448,7 +4421,7 @@
         <v/>
       </c>
     </row>
-    <row r="361" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="361" spans="16:31">
       <c r="P361" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5458,7 +4431,7 @@
         <v/>
       </c>
     </row>
-    <row r="362" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="362" spans="16:31">
       <c r="P362" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5468,7 +4441,7 @@
         <v/>
       </c>
     </row>
-    <row r="363" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="363" spans="16:31">
       <c r="P363" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5478,7 +4451,7 @@
         <v/>
       </c>
     </row>
-    <row r="364" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="364" spans="16:31">
       <c r="P364" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5488,7 +4461,7 @@
         <v/>
       </c>
     </row>
-    <row r="365" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="365" spans="16:31">
       <c r="P365" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5498,7 +4471,7 @@
         <v/>
       </c>
     </row>
-    <row r="366" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="366" spans="16:31">
       <c r="P366" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5508,7 +4481,7 @@
         <v/>
       </c>
     </row>
-    <row r="367" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="367" spans="16:31">
       <c r="P367" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5518,7 +4491,7 @@
         <v/>
       </c>
     </row>
-    <row r="368" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="368" spans="16:31">
       <c r="P368" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5528,7 +4501,7 @@
         <v/>
       </c>
     </row>
-    <row r="369" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="369" spans="16:31">
       <c r="P369" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5538,7 +4511,7 @@
         <v/>
       </c>
     </row>
-    <row r="370" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="370" spans="16:31">
       <c r="P370" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5548,7 +4521,7 @@
         <v/>
       </c>
     </row>
-    <row r="371" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="371" spans="16:31">
       <c r="P371" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5558,7 +4531,7 @@
         <v/>
       </c>
     </row>
-    <row r="372" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="372" spans="16:31">
       <c r="P372" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5568,7 +4541,7 @@
         <v/>
       </c>
     </row>
-    <row r="373" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="373" spans="16:31">
       <c r="P373" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5578,7 +4551,7 @@
         <v/>
       </c>
     </row>
-    <row r="374" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="374" spans="16:31">
       <c r="P374" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5588,7 +4561,7 @@
         <v/>
       </c>
     </row>
-    <row r="375" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="375" spans="16:31">
       <c r="P375" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5598,7 +4571,7 @@
         <v/>
       </c>
     </row>
-    <row r="376" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="376" spans="16:31">
       <c r="P376" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5608,7 +4581,7 @@
         <v/>
       </c>
     </row>
-    <row r="377" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="377" spans="16:31">
       <c r="P377" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5618,7 +4591,7 @@
         <v/>
       </c>
     </row>
-    <row r="378" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="378" spans="16:31">
       <c r="P378" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5628,7 +4601,7 @@
         <v/>
       </c>
     </row>
-    <row r="379" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="379" spans="16:31">
       <c r="P379" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5638,7 +4611,7 @@
         <v/>
       </c>
     </row>
-    <row r="380" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="380" spans="16:31">
       <c r="P380" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5648,7 +4621,7 @@
         <v/>
       </c>
     </row>
-    <row r="381" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="381" spans="16:31">
       <c r="P381" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5658,7 +4631,7 @@
         <v/>
       </c>
     </row>
-    <row r="382" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="382" spans="16:31">
       <c r="P382" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5668,7 +4641,7 @@
         <v/>
       </c>
     </row>
-    <row r="383" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="383" spans="16:31">
       <c r="P383" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5678,7 +4651,7 @@
         <v/>
       </c>
     </row>
-    <row r="384" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="384" spans="16:31">
       <c r="P384" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5688,7 +4661,7 @@
         <v/>
       </c>
     </row>
-    <row r="385" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="385" spans="16:31">
       <c r="P385" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -5698,7 +4671,7 @@
         <v/>
       </c>
     </row>
-    <row r="386" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="386" spans="16:31">
       <c r="P386" t="str">
         <f t="shared" ref="P386:P449" si="12">IF(AND(N386&lt;&gt;"",O386&lt;&gt;""),N386&amp;" x "&amp;O386,"")</f>
         <v/>
@@ -5708,7 +4681,7 @@
         <v/>
       </c>
     </row>
-    <row r="387" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="387" spans="16:31">
       <c r="P387" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5718,7 +4691,7 @@
         <v/>
       </c>
     </row>
-    <row r="388" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="388" spans="16:31">
       <c r="P388" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5728,7 +4701,7 @@
         <v/>
       </c>
     </row>
-    <row r="389" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="389" spans="16:31">
       <c r="P389" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5738,7 +4711,7 @@
         <v/>
       </c>
     </row>
-    <row r="390" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="390" spans="16:31">
       <c r="P390" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5748,7 +4721,7 @@
         <v/>
       </c>
     </row>
-    <row r="391" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="391" spans="16:31">
       <c r="P391" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5758,7 +4731,7 @@
         <v/>
       </c>
     </row>
-    <row r="392" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="392" spans="16:31">
       <c r="P392" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5768,7 +4741,7 @@
         <v/>
       </c>
     </row>
-    <row r="393" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="393" spans="16:31">
       <c r="P393" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5778,7 +4751,7 @@
         <v/>
       </c>
     </row>
-    <row r="394" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="394" spans="16:31">
       <c r="P394" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5788,7 +4761,7 @@
         <v/>
       </c>
     </row>
-    <row r="395" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="395" spans="16:31">
       <c r="P395" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5798,7 +4771,7 @@
         <v/>
       </c>
     </row>
-    <row r="396" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="396" spans="16:31">
       <c r="P396" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5808,7 +4781,7 @@
         <v/>
       </c>
     </row>
-    <row r="397" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="397" spans="16:31">
       <c r="P397" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5818,7 +4791,7 @@
         <v/>
       </c>
     </row>
-    <row r="398" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="398" spans="16:31">
       <c r="P398" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5828,7 +4801,7 @@
         <v/>
       </c>
     </row>
-    <row r="399" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="399" spans="16:31">
       <c r="P399" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5838,7 +4811,7 @@
         <v/>
       </c>
     </row>
-    <row r="400" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="400" spans="16:31">
       <c r="P400" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5848,7 +4821,7 @@
         <v/>
       </c>
     </row>
-    <row r="401" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="401" spans="16:31">
       <c r="P401" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5858,7 +4831,7 @@
         <v/>
       </c>
     </row>
-    <row r="402" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="402" spans="16:31">
       <c r="P402" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5868,7 +4841,7 @@
         <v/>
       </c>
     </row>
-    <row r="403" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="403" spans="16:31">
       <c r="P403" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5878,7 +4851,7 @@
         <v/>
       </c>
     </row>
-    <row r="404" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="404" spans="16:31">
       <c r="P404" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5888,7 +4861,7 @@
         <v/>
       </c>
     </row>
-    <row r="405" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="405" spans="16:31">
       <c r="P405" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5898,7 +4871,7 @@
         <v/>
       </c>
     </row>
-    <row r="406" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="406" spans="16:31">
       <c r="P406" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5908,7 +4881,7 @@
         <v/>
       </c>
     </row>
-    <row r="407" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="407" spans="16:31">
       <c r="P407" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5918,7 +4891,7 @@
         <v/>
       </c>
     </row>
-    <row r="408" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="408" spans="16:31">
       <c r="P408" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5928,7 +4901,7 @@
         <v/>
       </c>
     </row>
-    <row r="409" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="409" spans="16:31">
       <c r="P409" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5938,7 +4911,7 @@
         <v/>
       </c>
     </row>
-    <row r="410" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="410" spans="16:31">
       <c r="P410" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5948,7 +4921,7 @@
         <v/>
       </c>
     </row>
-    <row r="411" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="411" spans="16:31">
       <c r="P411" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5958,7 +4931,7 @@
         <v/>
       </c>
     </row>
-    <row r="412" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="412" spans="16:31">
       <c r="P412" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5968,7 +4941,7 @@
         <v/>
       </c>
     </row>
-    <row r="413" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="413" spans="16:31">
       <c r="P413" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5978,7 +4951,7 @@
         <v/>
       </c>
     </row>
-    <row r="414" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="414" spans="16:31">
       <c r="P414" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5988,7 +4961,7 @@
         <v/>
       </c>
     </row>
-    <row r="415" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="415" spans="16:31">
       <c r="P415" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -5998,7 +4971,7 @@
         <v/>
       </c>
     </row>
-    <row r="416" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="416" spans="16:31">
       <c r="P416" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6008,7 +4981,7 @@
         <v/>
       </c>
     </row>
-    <row r="417" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="417" spans="16:31">
       <c r="P417" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6018,7 +4991,7 @@
         <v/>
       </c>
     </row>
-    <row r="418" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="418" spans="16:31">
       <c r="P418" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6028,7 +5001,7 @@
         <v/>
       </c>
     </row>
-    <row r="419" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="419" spans="16:31">
       <c r="P419" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6038,7 +5011,7 @@
         <v/>
       </c>
     </row>
-    <row r="420" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="420" spans="16:31">
       <c r="P420" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6048,7 +5021,7 @@
         <v/>
       </c>
     </row>
-    <row r="421" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="421" spans="16:31">
       <c r="P421" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6058,7 +5031,7 @@
         <v/>
       </c>
     </row>
-    <row r="422" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="422" spans="16:31">
       <c r="P422" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6068,7 +5041,7 @@
         <v/>
       </c>
     </row>
-    <row r="423" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="423" spans="16:31">
       <c r="P423" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6078,7 +5051,7 @@
         <v/>
       </c>
     </row>
-    <row r="424" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="424" spans="16:31">
       <c r="P424" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6088,7 +5061,7 @@
         <v/>
       </c>
     </row>
-    <row r="425" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="425" spans="16:31">
       <c r="P425" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6098,7 +5071,7 @@
         <v/>
       </c>
     </row>
-    <row r="426" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="426" spans="16:31">
       <c r="P426" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6108,7 +5081,7 @@
         <v/>
       </c>
     </row>
-    <row r="427" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="427" spans="16:31">
       <c r="P427" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6118,7 +5091,7 @@
         <v/>
       </c>
     </row>
-    <row r="428" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="428" spans="16:31">
       <c r="P428" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6128,7 +5101,7 @@
         <v/>
       </c>
     </row>
-    <row r="429" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="429" spans="16:31">
       <c r="P429" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6138,7 +5111,7 @@
         <v/>
       </c>
     </row>
-    <row r="430" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="430" spans="16:31">
       <c r="P430" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6148,7 +5121,7 @@
         <v/>
       </c>
     </row>
-    <row r="431" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="431" spans="16:31">
       <c r="P431" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6158,7 +5131,7 @@
         <v/>
       </c>
     </row>
-    <row r="432" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="432" spans="16:31">
       <c r="P432" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6168,7 +5141,7 @@
         <v/>
       </c>
     </row>
-    <row r="433" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="433" spans="16:31">
       <c r="P433" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6178,7 +5151,7 @@
         <v/>
       </c>
     </row>
-    <row r="434" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="434" spans="16:31">
       <c r="P434" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6188,7 +5161,7 @@
         <v/>
       </c>
     </row>
-    <row r="435" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="435" spans="16:31">
       <c r="P435" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6198,7 +5171,7 @@
         <v/>
       </c>
     </row>
-    <row r="436" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="436" spans="16:31">
       <c r="P436" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6208,7 +5181,7 @@
         <v/>
       </c>
     </row>
-    <row r="437" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="437" spans="16:31">
       <c r="P437" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6218,7 +5191,7 @@
         <v/>
       </c>
     </row>
-    <row r="438" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="438" spans="16:31">
       <c r="P438" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6228,7 +5201,7 @@
         <v/>
       </c>
     </row>
-    <row r="439" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="439" spans="16:31">
       <c r="P439" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6238,7 +5211,7 @@
         <v/>
       </c>
     </row>
-    <row r="440" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="440" spans="16:31">
       <c r="P440" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6248,7 +5221,7 @@
         <v/>
       </c>
     </row>
-    <row r="441" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="441" spans="16:31">
       <c r="P441" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6258,7 +5231,7 @@
         <v/>
       </c>
     </row>
-    <row r="442" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="442" spans="16:31">
       <c r="P442" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6268,7 +5241,7 @@
         <v/>
       </c>
     </row>
-    <row r="443" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="443" spans="16:31">
       <c r="P443" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6278,7 +5251,7 @@
         <v/>
       </c>
     </row>
-    <row r="444" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="444" spans="16:31">
       <c r="P444" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6288,7 +5261,7 @@
         <v/>
       </c>
     </row>
-    <row r="445" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="445" spans="16:31">
       <c r="P445" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6298,7 +5271,7 @@
         <v/>
       </c>
     </row>
-    <row r="446" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="446" spans="16:31">
       <c r="P446" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6308,7 +5281,7 @@
         <v/>
       </c>
     </row>
-    <row r="447" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="447" spans="16:31">
       <c r="P447" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6318,7 +5291,7 @@
         <v/>
       </c>
     </row>
-    <row r="448" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="448" spans="16:31">
       <c r="P448" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6328,7 +5301,7 @@
         <v/>
       </c>
     </row>
-    <row r="449" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="449" spans="16:31">
       <c r="P449" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -6338,7 +5311,7 @@
         <v/>
       </c>
     </row>
-    <row r="450" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="450" spans="16:31">
       <c r="P450" t="str">
         <f t="shared" ref="P450:P500" si="14">IF(AND(N450&lt;&gt;"",O450&lt;&gt;""),N450&amp;" x "&amp;O450,"")</f>
         <v/>
@@ -6348,7 +5321,7 @@
         <v/>
       </c>
     </row>
-    <row r="451" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="451" spans="16:31">
       <c r="P451" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6358,7 +5331,7 @@
         <v/>
       </c>
     </row>
-    <row r="452" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="452" spans="16:31">
       <c r="P452" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6368,7 +5341,7 @@
         <v/>
       </c>
     </row>
-    <row r="453" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="453" spans="16:31">
       <c r="P453" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6378,7 +5351,7 @@
         <v/>
       </c>
     </row>
-    <row r="454" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="454" spans="16:31">
       <c r="P454" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6388,7 +5361,7 @@
         <v/>
       </c>
     </row>
-    <row r="455" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="455" spans="16:31">
       <c r="P455" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6398,7 +5371,7 @@
         <v/>
       </c>
     </row>
-    <row r="456" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="456" spans="16:31">
       <c r="P456" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6408,7 +5381,7 @@
         <v/>
       </c>
     </row>
-    <row r="457" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="457" spans="16:31">
       <c r="P457" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6418,7 +5391,7 @@
         <v/>
       </c>
     </row>
-    <row r="458" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="458" spans="16:31">
       <c r="P458" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6428,7 +5401,7 @@
         <v/>
       </c>
     </row>
-    <row r="459" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="459" spans="16:31">
       <c r="P459" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6438,7 +5411,7 @@
         <v/>
       </c>
     </row>
-    <row r="460" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="460" spans="16:31">
       <c r="P460" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6448,7 +5421,7 @@
         <v/>
       </c>
     </row>
-    <row r="461" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="461" spans="16:31">
       <c r="P461" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6458,7 +5431,7 @@
         <v/>
       </c>
     </row>
-    <row r="462" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="462" spans="16:31">
       <c r="P462" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6468,7 +5441,7 @@
         <v/>
       </c>
     </row>
-    <row r="463" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="463" spans="16:31">
       <c r="P463" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6478,7 +5451,7 @@
         <v/>
       </c>
     </row>
-    <row r="464" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="464" spans="16:31">
       <c r="P464" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6488,7 +5461,7 @@
         <v/>
       </c>
     </row>
-    <row r="465" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="465" spans="16:31">
       <c r="P465" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6498,7 +5471,7 @@
         <v/>
       </c>
     </row>
-    <row r="466" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="466" spans="16:31">
       <c r="P466" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6508,7 +5481,7 @@
         <v/>
       </c>
     </row>
-    <row r="467" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="467" spans="16:31">
       <c r="P467" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6518,7 +5491,7 @@
         <v/>
       </c>
     </row>
-    <row r="468" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="468" spans="16:31">
       <c r="P468" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6528,7 +5501,7 @@
         <v/>
       </c>
     </row>
-    <row r="469" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="469" spans="16:31">
       <c r="P469" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6538,7 +5511,7 @@
         <v/>
       </c>
     </row>
-    <row r="470" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="470" spans="16:31">
       <c r="P470" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6548,7 +5521,7 @@
         <v/>
       </c>
     </row>
-    <row r="471" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="471" spans="16:31">
       <c r="P471" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6558,7 +5531,7 @@
         <v/>
       </c>
     </row>
-    <row r="472" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="472" spans="16:31">
       <c r="P472" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6568,7 +5541,7 @@
         <v/>
       </c>
     </row>
-    <row r="473" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="473" spans="16:31">
       <c r="P473" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6578,7 +5551,7 @@
         <v/>
       </c>
     </row>
-    <row r="474" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="474" spans="16:31">
       <c r="P474" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6588,7 +5561,7 @@
         <v/>
       </c>
     </row>
-    <row r="475" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="475" spans="16:31">
       <c r="P475" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6598,7 +5571,7 @@
         <v/>
       </c>
     </row>
-    <row r="476" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="476" spans="16:31">
       <c r="P476" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6608,7 +5581,7 @@
         <v/>
       </c>
     </row>
-    <row r="477" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="477" spans="16:31">
       <c r="P477" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6618,7 +5591,7 @@
         <v/>
       </c>
     </row>
-    <row r="478" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="478" spans="16:31">
       <c r="P478" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6628,7 +5601,7 @@
         <v/>
       </c>
     </row>
-    <row r="479" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="479" spans="16:31">
       <c r="P479" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6638,7 +5611,7 @@
         <v/>
       </c>
     </row>
-    <row r="480" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="480" spans="16:31">
       <c r="P480" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6648,7 +5621,7 @@
         <v/>
       </c>
     </row>
-    <row r="481" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="481" spans="16:31">
       <c r="P481" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6658,7 +5631,7 @@
         <v/>
       </c>
     </row>
-    <row r="482" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="482" spans="16:31">
       <c r="P482" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6668,7 +5641,7 @@
         <v/>
       </c>
     </row>
-    <row r="483" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="483" spans="16:31">
       <c r="P483" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6678,7 +5651,7 @@
         <v/>
       </c>
     </row>
-    <row r="484" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="484" spans="16:31">
       <c r="P484" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6688,7 +5661,7 @@
         <v/>
       </c>
     </row>
-    <row r="485" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="485" spans="16:31">
       <c r="P485" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6698,7 +5671,7 @@
         <v/>
       </c>
     </row>
-    <row r="486" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="486" spans="16:31">
       <c r="P486" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6708,7 +5681,7 @@
         <v/>
       </c>
     </row>
-    <row r="487" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="487" spans="16:31">
       <c r="P487" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6718,7 +5691,7 @@
         <v/>
       </c>
     </row>
-    <row r="488" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="488" spans="16:31">
       <c r="P488" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6728,7 +5701,7 @@
         <v/>
       </c>
     </row>
-    <row r="489" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="489" spans="16:31">
       <c r="P489" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6738,7 +5711,7 @@
         <v/>
       </c>
     </row>
-    <row r="490" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="490" spans="16:31">
       <c r="P490" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6748,7 +5721,7 @@
         <v/>
       </c>
     </row>
-    <row r="491" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="491" spans="16:31">
       <c r="P491" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6758,7 +5731,7 @@
         <v/>
       </c>
     </row>
-    <row r="492" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="492" spans="16:31">
       <c r="P492" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6768,7 +5741,7 @@
         <v/>
       </c>
     </row>
-    <row r="493" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="493" spans="16:31">
       <c r="P493" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6778,7 +5751,7 @@
         <v/>
       </c>
     </row>
-    <row r="494" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="494" spans="16:31">
       <c r="P494" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6788,7 +5761,7 @@
         <v/>
       </c>
     </row>
-    <row r="495" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="495" spans="16:31">
       <c r="P495" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6798,7 +5771,7 @@
         <v/>
       </c>
     </row>
-    <row r="496" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="496" spans="16:31">
       <c r="P496" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6808,7 +5781,7 @@
         <v/>
       </c>
     </row>
-    <row r="497" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="497" spans="16:31">
       <c r="P497" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6818,7 +5791,7 @@
         <v/>
       </c>
     </row>
-    <row r="498" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="498" spans="16:31">
       <c r="P498" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6828,7 +5801,7 @@
         <v/>
       </c>
     </row>
-    <row r="499" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="499" spans="16:31">
       <c r="P499" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6838,7 +5811,7 @@
         <v/>
       </c>
     </row>
-    <row r="500" spans="16:31" x14ac:dyDescent="0.3">
+    <row r="500" spans="16:31">
       <c r="P500" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6850,7 +5823,21 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="AG1:AG2"/>
+    <mergeCell ref="AF1:AF2"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="U1:U2"/>
+    <mergeCell ref="V1:V2"/>
+    <mergeCell ref="W1:W2"/>
+    <mergeCell ref="X1:X2"/>
+    <mergeCell ref="Y1:Y2"/>
+    <mergeCell ref="AA1:AA2"/>
+    <mergeCell ref="AB1:AB2"/>
+    <mergeCell ref="AE1:AE2"/>
+    <mergeCell ref="T1:T2"/>
+    <mergeCell ref="Z1:Z2"/>
     <mergeCell ref="P1:P2"/>
     <mergeCell ref="AC1:AD1"/>
     <mergeCell ref="A1:A2"/>
@@ -6867,21 +5854,7 @@
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
-    <mergeCell ref="AG1:AG2"/>
-    <mergeCell ref="AF1:AF2"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="U1:U2"/>
-    <mergeCell ref="V1:V2"/>
-    <mergeCell ref="W1:W2"/>
-    <mergeCell ref="X1:X2"/>
-    <mergeCell ref="Y1:Y2"/>
-    <mergeCell ref="AA1:AA2"/>
-    <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AE1:AE2"/>
-    <mergeCell ref="T1:T2"/>
-    <mergeCell ref="Z1:Z2"/>
+    <mergeCell ref="L1:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="V4:V500">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -6960,108 +5933,108 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="D6" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
